--- a/04-终极版择校/全国408_085410双非热度版_终极版_20260826.xlsx
+++ b/04-终极版择校/全国408_085410双非热度版_终极版_20260826.xlsx
@@ -15711,15 +15711,17 @@
           <t>电子信息-计算机</t>
         </is>
       </c>
-      <c r="H117" s="2" t="n"/>
+      <c r="H117" s="2" t="n">
+        <v>264</v>
+      </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>— / — / — / —</t>
+          <t>— / 273 / 281 / 264</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -15776,7 +15778,7 @@
       </c>
       <c r="W117" s="2" t="n"/>
       <c r="X117" s="2" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Y117" s="2" t="inlineStr">
         <is>
@@ -27654,12 +27656,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>江西中医药大学</t>
+          <t>海南师范大学</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -27669,7 +27671,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -27692,7 +27694,7 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -27702,7 +27704,7 @@
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -27712,12 +27714,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>海南师范大学</t>
+          <t>湖北汽车工业学院</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -27727,7 +27729,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>智能网联汽车学院</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -27750,7 +27752,7 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -27760,7 +27762,7 @@
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -27770,12 +27772,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>湖北汽车工业学院</t>
+          <t>西安建筑科技大学</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>西北</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -27785,7 +27787,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>智能网联汽车学院</t>
+          <t>信息与控制工程学院</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -27828,12 +27830,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>西安建筑科技大学</t>
+          <t>华北理工大学</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -27843,40 +27845,44 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>信息与控制工程学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="n"/>
+          <t>22408</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>264</v>
+      </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="J79" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>42</v>
+      </c>
       <c r="K79" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅真AI方向</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>2026目录拟招14，408；复试线未单独查到</t>
         </is>
       </c>
     </row>
@@ -27886,7 +27892,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>华北理工大学</t>
+          <t>呼和浩特民族学院</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -27901,16 +27907,16 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机与信息技术学院</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="G80" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
@@ -27918,17 +27924,17 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>21</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>✅真AI方向</t>
+          <t>❓未注明</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -27938,7 +27944,7 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>2026目录拟招14，408；复试线未单独查到</t>
+          <t>B区国家线；调剂细则要求业务课408</t>
         </is>
       </c>
     </row>
@@ -27948,12 +27954,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>呼和浩特民族学院</t>
+          <t>桂林电子科技大学</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -27963,12 +27969,12 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息技术学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="G81" s="2" t="n">
@@ -27980,17 +27986,17 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>21</v>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>❓未注明</t>
+          <t>✅真AI方向</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -28000,7 +28006,7 @@
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>B区国家线；调剂细则要求业务课408</t>
+          <t>B区国家线254；一志愿上线19，调剂缺口较大</t>
         </is>
       </c>
     </row>
@@ -28010,12 +28016,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>桂林电子科技大学</t>
+          <t>西南民族大学</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -28025,7 +28031,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -28034,7 +28040,7 @@
         </is>
       </c>
       <c r="G82" s="2" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
@@ -28045,7 +28051,7 @@
         <v>9</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>21</v>
@@ -28062,7 +28068,7 @@
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>B区国家线254；一志愿上线19，调剂缺口较大</t>
+          <t>2026调剂公告含085410，408；拟录取附件反爬</t>
         </is>
       </c>
     </row>
@@ -28072,12 +28078,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>西南民族大学</t>
+          <t>新疆农业大学</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>西北</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -28087,7 +28093,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -28096,7 +28102,7 @@
         </is>
       </c>
       <c r="G83" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -28104,17 +28110,17 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>21</v>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>✅真AI方向</t>
+          <t>❓未注明</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -28124,7 +28130,7 @@
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>2026调剂公告含085410，408；拟录取附件反爬</t>
+          <t>2027由867数据结构改408（官方公告2026-07-09）；22408；B区线254，一志愿常需调剂</t>
         </is>
       </c>
     </row>
@@ -28134,12 +28140,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>新疆农业大学</t>
+          <t>北京电子科技学院</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -28149,44 +28155,42 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G84" s="2" t="n">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+18</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J84" s="2" t="n">
-        <v>36</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J84" s="2" t="n"/>
       <c r="K84" s="2" t="n">
         <v>21</v>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>❓未注明</t>
+          <t>⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>2027由867数据结构改408（官方公告2026-07-09）；22408；B区线254，一志愿常需调剂</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
     </row>
@@ -28196,12 +28200,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>北京电子科技学院</t>
+          <t>重庆科技大学</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -28211,42 +28215,44 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>计算机科学与工程学院（人工智能学院）</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="G85" s="2" t="n">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>+18</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J85" s="2" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="K85" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)；含电子信息</t>
+          <t>✅真AI方向</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
+          <t>22408（英二数二）；2026调剂约45人过线即录；复试笔试912程序设计综合；导师韩琦（医学影像/无人驾驶）；调剂9名额说明一志愿缺额</t>
         </is>
       </c>
     </row>
@@ -28256,12 +28262,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>重庆科技大学</t>
+          <t>安徽工业大学</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -28271,44 +28277,42 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与工程学院（人工智能学院）</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G86" s="2" t="n">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+30</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>44</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="J86" s="2" t="n"/>
       <c r="K86" s="2" t="n">
         <v>20</v>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>✅真AI方向</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>22408（英二数二）；2026调剂约45人过线即录；复试笔试912程序设计综合；导师韩琦（医学影像/无人驾驶）；调剂9名额说明一志愿缺额</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28322,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>安徽工业大学</t>
+          <t>杭州师范大学</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -28333,7 +28337,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>工学院</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -28342,15 +28346,15 @@
         </is>
       </c>
       <c r="G87" s="2" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>+30</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J87" s="2" t="n"/>
       <c r="K87" s="2" t="n">
@@ -28358,7 +28362,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -28368,7 +28372,7 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -28378,7 +28382,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>杭州师范大学</t>
+          <t>苏州科技大学</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -28393,7 +28397,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>工学院</t>
+          <t>电子与信息工程学院</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -28402,15 +28406,15 @@
         </is>
       </c>
       <c r="G88" s="2" t="n">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>+36</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="2" t="n">
@@ -28418,7 +28422,7 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
@@ -28428,7 +28432,7 @@
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容</t>
         </is>
       </c>
     </row>
@@ -28438,12 +28442,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>苏州科技大学</t>
+          <t>长沙理工大学</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -28453,7 +28457,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>电子与信息工程学院</t>
+          <t>计算机与通信工程学院</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -28462,15 +28466,15 @@
         </is>
       </c>
       <c r="G89" s="2" t="n">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>+36</t>
+          <t>+25</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J89" s="2" t="n"/>
       <c r="K89" s="2" t="n">
@@ -28478,7 +28482,7 @@
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -28488,7 +28492,7 @@
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -28498,12 +28502,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>长沙理工大学</t>
+          <t>厦门理工学院</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -28513,42 +28517,44 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>计算机与通信工程学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>非408</t>
         </is>
       </c>
       <c r="G90" s="2" t="n">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>+25</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="J90" s="2" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>42</v>
+      </c>
       <c r="K90" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>❓未注明</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>机构估算</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>2026复试线国家线，有调剂；2026目录中085410待核（疑似非408）</t>
         </is>
       </c>
     </row>
@@ -28558,12 +28564,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>厦门理工学院</t>
+          <t>中南林业科技大学</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -28573,44 +28579,42 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>低空经济学院</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>非408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G91" s="2" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+14</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J91" s="2" t="n">
-        <v>42</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="J91" s="2" t="n"/>
       <c r="K91" s="2" t="n">
         <v>19</v>
       </c>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>❓未注明</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>机构估算</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>2026复试线国家线，有调剂；2026目录中085410待核（疑似非408）</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -28620,12 +28624,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>中南林业科技大学</t>
+          <t>石家庄铁道大学</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -28635,7 +28639,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>低空经济学院</t>
+          <t>信息科学与技术学院</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -28644,11 +28648,11 @@
         </is>
       </c>
       <c r="G92" s="2" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>+14</t>
+          <t>+17</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -28660,7 +28664,7 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -28670,7 +28674,7 @@
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -28680,12 +28684,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>石家庄铁道大学</t>
+          <t>中国民用航空飞行学院</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -28695,42 +28699,44 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>信息科学与技术学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>+17</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I93" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="J93" s="2" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="K93" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>❓未注明</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>民航特色，2026一志愿不足有调剂；一志愿复试1人</t>
         </is>
       </c>
     </row>
@@ -28740,12 +28746,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>中国民用航空飞行学院</t>
+          <t>太原科技大学</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -28755,44 +28761,42 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+23</t>
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>40</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="J94" s="2" t="n"/>
       <c r="K94" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>❓未注明</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>民航特色，2026一志愿不足有调剂；一志愿复试1人</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -28802,12 +28806,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>太原科技大学</t>
+          <t>武汉工程大学</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -28817,7 +28821,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机科学与工程学院（人工智能学院）</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -28826,23 +28830,23 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>+23</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J95" s="2" t="n"/>
       <c r="K95" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
@@ -28852,7 +28856,7 @@
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -28862,12 +28866,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>武汉工程大学</t>
+          <t>天津职业技术师范大学</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -28877,7 +28881,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与工程学院（人工智能学院）</t>
+          <t>信息技术工程学院</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -28886,23 +28890,23 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>+17</t>
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J96" s="2" t="n"/>
       <c r="K96" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -28912,7 +28916,7 @@
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -28922,12 +28926,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>天津职业技术师范大学</t>
+          <t>上海海洋大学</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -28937,7 +28941,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>信息技术工程学院</t>
+          <t>信息学院</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -28946,23 +28950,23 @@
         </is>
       </c>
       <c r="G97" s="2" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>+17</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2" t="n"/>
       <c r="K97" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -28972,7 +28976,7 @@
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -28982,7 +28986,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>上海海洋大学</t>
+          <t>上海科技大学</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -28997,7 +29001,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>信息学院</t>
+          <t>信息科学与技术学院</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -29022,7 +29026,7 @@
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
@@ -29032,7 +29036,7 @@
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
     </row>
@@ -29042,7 +29046,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>上海科技大学</t>
+          <t>中国计量大学</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -29057,7 +29061,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>信息科学与技术学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -29066,11 +29070,11 @@
         </is>
       </c>
       <c r="G99" s="2" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
@@ -29082,7 +29086,7 @@
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
@@ -29092,7 +29096,7 @@
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -29102,7 +29106,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中国计量大学</t>
+          <t>南京财经大学</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -29117,7 +29121,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -29126,11 +29130,11 @@
         </is>
       </c>
       <c r="G100" s="2" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -29162,12 +29166,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>南京财经大学</t>
+          <t>天津农学院</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -29177,7 +29181,7 @@
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -29186,11 +29190,11 @@
         </is>
       </c>
       <c r="G101" s="2" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -29222,12 +29226,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>天津农学院</t>
+          <t>河南农业大学</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -29237,7 +29241,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>信息与管理科学学院</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -29262,7 +29266,7 @@
       </c>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -29272,7 +29276,7 @@
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -29282,7 +29286,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>河南农业大学</t>
+          <t>河南理工大学</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -29297,7 +29301,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>信息与管理科学学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -29306,15 +29310,15 @@
         </is>
       </c>
       <c r="G103" s="2" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J103" s="2" t="n"/>
       <c r="K103" s="2" t="n">
@@ -29342,12 +29346,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>河南理工大学</t>
+          <t>浙江农林大学</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -29357,7 +29361,7 @@
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>数学与计算机科学学院</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -29366,15 +29370,15 @@
         </is>
       </c>
       <c r="G104" s="2" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J104" s="2" t="n"/>
       <c r="K104" s="2" t="n">
@@ -29382,7 +29386,7 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -29392,7 +29396,7 @@
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -29402,12 +29406,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>浙江农林大学</t>
+          <t>西南石油大学</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -29417,7 +29421,7 @@
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>数学与计算机科学学院</t>
+          <t>计算机科学学院</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -29426,11 +29430,11 @@
         </is>
       </c>
       <c r="G105" s="2" t="n">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
@@ -29442,7 +29446,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -29452,7 +29456,7 @@
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -29462,12 +29466,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>西南石油大学</t>
+          <t>南华大学</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -29477,7 +29481,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>计算机科学学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -29486,19 +29490,19 @@
         </is>
       </c>
       <c r="G106" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J106" s="2" t="n"/>
       <c r="K106" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
@@ -29522,12 +29526,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>南华大学</t>
+          <t>广西民族大学</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -29537,7 +29541,7 @@
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -29546,11 +29550,11 @@
         </is>
       </c>
       <c r="G107" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
@@ -29562,7 +29566,7 @@
       </c>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
@@ -29572,7 +29576,7 @@
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -29582,12 +29586,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>广西民族大学</t>
+          <t>湘潭大学</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -29597,7 +29601,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机学院/网络空间安全学院</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -29610,7 +29614,7 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
@@ -29622,7 +29626,7 @@
       </c>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
       <c r="M108" s="2" t="inlineStr">
@@ -29632,7 +29636,7 @@
       </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
     </row>
@@ -29642,12 +29646,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>湘潭大学</t>
+          <t>上海电机学院</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -29657,7 +29661,7 @@
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>计算机学院/网络空间安全学院</t>
+          <t>电子信息学院</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -29674,15 +29678,15 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J109" s="2" t="n"/>
       <c r="K109" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)；含电子信息</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
@@ -29692,7 +29696,7 @@
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -29702,7 +29706,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>上海电机学院</t>
+          <t>江苏师范大学</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -29717,7 +29721,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>电子信息学院</t>
+          <t>智慧教育学院（计算机科学与技术学院）</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -29742,7 +29746,7 @@
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M110" s="2" t="inlineStr">
@@ -29752,7 +29756,7 @@
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -29762,7 +29766,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>江苏师范大学</t>
+          <t>江西财经大学</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -29777,7 +29781,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>智慧教育学院（计算机科学与技术学院）</t>
+          <t>计算机与人工智能学院+信息管理学院</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -29802,7 +29806,7 @@
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
@@ -29812,7 +29816,7 @@
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -29822,7 +29826,7 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>江西财经大学</t>
+          <t>浙江财经大学</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -29837,7 +29841,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院+信息管理学院</t>
+          <t>信息管理人工智能学院</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -29882,7 +29886,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>浙江财经大学</t>
+          <t>温州大学</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -29897,7 +29901,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>信息管理人工智能学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -29942,7 +29946,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>温州大学</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -29957,7 +29961,7 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -29966,23 +29970,23 @@
         </is>
       </c>
       <c r="G114" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J114" s="2" t="n"/>
       <c r="K114" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -29992,7 +29996,7 @@
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -30002,12 +30006,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>佛山大学</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -30017,7 +30021,7 @@
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>电子信息工程学院</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -30026,11 +30030,11 @@
         </is>
       </c>
       <c r="G115" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
@@ -30042,7 +30046,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -30052,7 +30056,7 @@
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -30062,12 +30066,12 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>佛山大学</t>
+          <t>天津师范大学</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -30077,7 +30081,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>电子信息工程学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -30086,11 +30090,11 @@
         </is>
       </c>
       <c r="G116" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
@@ -30122,12 +30126,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>天津师范大学</t>
+          <t>安徽建筑大学</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -30137,7 +30141,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>电子与信息工程学院</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -30146,11 +30150,11 @@
         </is>
       </c>
       <c r="G117" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
@@ -30182,7 +30186,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>安徽建筑大学</t>
+          <t>江西理工大学</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -30197,7 +30201,7 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>电子与信息工程学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -30206,11 +30210,11 @@
         </is>
       </c>
       <c r="G118" s="2" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
@@ -30222,7 +30226,7 @@
       </c>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
@@ -30232,7 +30236,7 @@
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -30242,7 +30246,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>江西理工大学</t>
+          <t>浙江工业大学</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -30257,7 +30261,7 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>地理信息学院</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -30266,11 +30270,11 @@
         </is>
       </c>
       <c r="G119" s="2" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
@@ -30282,7 +30286,7 @@
       </c>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="M119" s="2" t="inlineStr">
@@ -30292,7 +30296,7 @@
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -30302,7 +30306,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>浙江工业大学</t>
+          <t>浙江科技大学</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -30317,7 +30321,7 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>地理信息学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -30326,11 +30330,11 @@
         </is>
       </c>
       <c r="G120" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -30342,7 +30346,7 @@
       </c>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
@@ -30352,7 +30356,7 @@
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -30362,12 +30366,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>浙江科技大学</t>
+          <t>西南科技大学</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -30422,12 +30426,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>西南科技大学</t>
+          <t>中南民族大学</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -30437,7 +30441,7 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -30454,15 +30458,15 @@
         </is>
       </c>
       <c r="I122" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J122" s="2" t="n"/>
       <c r="K122" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
@@ -30472,7 +30476,7 @@
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -30482,12 +30486,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>中南民族大学</t>
+          <t>中国民航大学</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -30497,7 +30501,7 @@
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>电子信息与自动化学院</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -30542,7 +30546,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>中国民航大学</t>
+          <t>北京印刷学院</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -30557,7 +30561,7 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>电子信息与自动化学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -30582,7 +30586,7 @@
       </c>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
@@ -30592,7 +30596,7 @@
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -30602,7 +30606,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>北京印刷学院</t>
+          <t>北京工商大学</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -30617,7 +30621,7 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -30662,7 +30666,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>北京工商大学</t>
+          <t>北京物资学院</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -30702,7 +30706,7 @@
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
@@ -30712,7 +30716,7 @@
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -30722,7 +30726,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>北京物资学院</t>
+          <t>北京联合大学</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -30737,7 +30741,7 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>智慧城市学院</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -30762,7 +30766,7 @@
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
@@ -30772,7 +30776,7 @@
       </c>
       <c r="N127" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -30782,7 +30786,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>北京联合大学</t>
+          <t>天津财经大学</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -30797,7 +30801,7 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>智慧城市学院</t>
+          <t>理工学院</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -30822,7 +30826,7 @@
       </c>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
@@ -30832,7 +30836,7 @@
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -30842,12 +30846,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>天津财经大学</t>
+          <t>安徽农业大学</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -30857,7 +30861,7 @@
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>理工学院</t>
+          <t>信息与计算机学院</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -30882,7 +30886,7 @@
       </c>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M129" s="2" t="inlineStr">
@@ -30892,7 +30896,7 @@
       </c>
       <c r="N129" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -30902,7 +30906,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>安徽农业大学</t>
+          <t>安徽理工大学</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -30917,7 +30921,7 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>信息与计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -30942,7 +30946,7 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
@@ -30952,7 +30956,7 @@
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -30962,7 +30966,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>安徽理工大学</t>
+          <t>山东工商学院</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -30977,7 +30981,7 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -31002,7 +31006,7 @@
       </c>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M131" s="2" t="inlineStr">
@@ -31012,7 +31016,7 @@
       </c>
       <c r="N131" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -31022,12 +31026,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>山东工商学院</t>
+          <t>山西大学</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -31037,7 +31041,7 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机与信息技术学院</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -31062,7 +31066,7 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
@@ -31072,7 +31076,7 @@
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -31082,12 +31086,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>山西大学</t>
+          <t>广西师范大学</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -31097,7 +31101,7 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息技术学院</t>
+          <t>计算机科学与信息工程学院</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -31106,7 +31110,7 @@
         </is>
       </c>
       <c r="G133" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -31122,7 +31126,7 @@
       </c>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M133" s="2" t="inlineStr">
@@ -31132,7 +31136,7 @@
       </c>
       <c r="N133" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -31142,12 +31146,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>广西师范大学</t>
+          <t>成都大学</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -31157,7 +31161,7 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与信息工程学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -31166,11 +31170,11 @@
         </is>
       </c>
       <c r="G134" s="2" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="I134" s="2" t="n">
@@ -31202,12 +31206,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>成都大学</t>
+          <t>桂林理工大学</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -31217,7 +31221,7 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>计算机科学与工程学院</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -31226,11 +31230,11 @@
         </is>
       </c>
       <c r="G135" s="2" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
@@ -31242,7 +31246,7 @@
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="M135" s="2" t="inlineStr">
@@ -31252,7 +31256,7 @@
       </c>
       <c r="N135" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -31262,12 +31266,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>桂林理工大学</t>
+          <t>武汉纺织大学</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -31277,7 +31281,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -31286,7 +31290,7 @@
         </is>
       </c>
       <c r="G136" s="2" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -31322,12 +31326,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>武汉纺织大学</t>
+          <t>江西中医药大学</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -31337,7 +31341,7 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -31362,7 +31366,7 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
@@ -31372,7 +31376,7 @@
       </c>
       <c r="N137" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -36802,17 +36806,17 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>江西中医药大学</t>
+          <t>华北理工大学</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -36822,40 +36826,44 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="n"/>
+          <t>22408</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>264</v>
+      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="M62" s="2" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>42</v>
+      </c>
       <c r="N62" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅真AI方向</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>2026目录拟招14，408；复试线未单独查到</t>
         </is>
       </c>
     </row>
@@ -36875,12 +36883,12 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>华北理工大学</t>
+          <t>呼和浩特民族学院</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -36895,16 +36903,16 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机与信息技术学院</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
@@ -36912,17 +36920,17 @@
         </is>
       </c>
       <c r="L63" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="N63" s="2" t="n">
         <v>21</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>✅真AI方向</t>
+          <t>❓未注明</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -36932,7 +36940,7 @@
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>2026目录拟招14，408；复试线未单独查到</t>
+          <t>B区国家线；调剂细则要求业务课408</t>
         </is>
       </c>
     </row>
@@ -36952,12 +36960,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>呼和浩特民族学院</t>
+          <t>北京电子科技学院</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -36972,44 +36980,42 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息技术学院</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+18</t>
         </is>
       </c>
       <c r="L64" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>34</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n">
         <v>21</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>❓未注明</t>
+          <t>⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>B区国家线；调剂细则要求业务课408</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
     </row>
@@ -37029,17 +37035,17 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>北京电子科技学院</t>
+          <t>安徽工业大学</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -37049,7 +37055,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -37058,23 +37064,23 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>+18</t>
+          <t>+30</t>
         </is>
       </c>
       <c r="L65" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M65" s="2" t="n"/>
       <c r="N65" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)；含电子信息</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -37084,7 +37090,7 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -37104,12 +37110,12 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>安徽工业大学</t>
+          <t>杭州师范大学</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -37124,7 +37130,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>工学院</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -37133,15 +37139,15 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>+30</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M66" s="2" t="n"/>
       <c r="N66" s="2" t="n">
@@ -37149,7 +37155,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -37159,7 +37165,7 @@
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -37179,12 +37185,12 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>杭州师范大学</t>
+          <t>苏州科技大学</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -37199,7 +37205,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>工学院</t>
+          <t>电子与信息工程学院</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -37208,15 +37214,15 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>+36</t>
         </is>
       </c>
       <c r="L67" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M67" s="2" t="n"/>
       <c r="N67" s="2" t="n">
@@ -37224,7 +37230,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -37234,7 +37240,7 @@
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容</t>
         </is>
       </c>
     </row>
@@ -37254,12 +37260,12 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>苏州科技大学</t>
+          <t>厦门理工学院</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -37274,42 +37280,44 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>电子与信息工程学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>非408</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>+36</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="M68" s="2" t="n"/>
+        <v>9</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>42</v>
+      </c>
       <c r="N68" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容</t>
+          <t>❓未注明</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>机构估算</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容</t>
+          <t>2026复试线国家线，有调剂；2026目录中085410待核（疑似非408）</t>
         </is>
       </c>
     </row>
@@ -37329,17 +37337,17 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>厦门理工学院</t>
+          <t>石家庄铁道大学</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -37349,44 +37357,42 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>信息科学与技术学院</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>非408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+17</t>
         </is>
       </c>
       <c r="L69" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>42</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="M69" s="2" t="n"/>
       <c r="N69" s="2" t="n">
         <v>19</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>❓未注明</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>机构估算</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
         <is>
-          <t>2026复试线国家线，有调剂；2026目录中085410待核（疑似非408）</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -37406,12 +37412,12 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>石家庄铁道大学</t>
+          <t>太原科技大学</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -37426,7 +37432,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>信息科学与技术学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -37435,23 +37441,23 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>+17</t>
+          <t>+23</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -37461,7 +37467,7 @@
       </c>
       <c r="Q70" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -37481,12 +37487,12 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>太原科技大学</t>
+          <t>天津职业技术师范大学</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -37501,7 +37507,7 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>信息技术工程学院</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -37510,23 +37516,23 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>+23</t>
+          <t>+17</t>
         </is>
       </c>
       <c r="L71" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M71" s="2" t="n"/>
       <c r="N71" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -37536,7 +37542,7 @@
       </c>
       <c r="Q71" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -37556,17 +37562,17 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>天津职业技术师范大学</t>
+          <t>上海海洋大学</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -37576,7 +37582,7 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>信息技术工程学院</t>
+          <t>信息学院</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -37585,23 +37591,23 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>+17</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M72" s="2" t="n"/>
       <c r="N72" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -37611,7 +37617,7 @@
       </c>
       <c r="Q72" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -37631,7 +37637,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>上海海洋大学</t>
+          <t>上海科技大学</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -37651,7 +37657,7 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>信息学院</t>
+          <t>信息科学与技术学院</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -37676,7 +37682,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -37686,7 +37692,7 @@
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
         </is>
       </c>
     </row>
@@ -37706,12 +37712,12 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>上海科技大学</t>
+          <t>中国计量大学</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -37726,7 +37732,7 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>信息科学与技术学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -37735,11 +37741,11 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="L74" s="2" t="n">
@@ -37751,7 +37757,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -37761,7 +37767,7 @@
       </c>
       <c r="Q74" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -37781,12 +37787,12 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>中国计量大学</t>
+          <t>南京财经大学</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -37801,7 +37807,7 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -37810,11 +37816,11 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="L75" s="2" t="n">
@@ -37856,17 +37862,17 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>南京财经大学</t>
+          <t>天津农学院</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -37876,7 +37882,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -37885,11 +37891,11 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L76" s="2" t="n">
@@ -37931,17 +37937,17 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>天津农学院</t>
+          <t>浙江农林大学</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -37951,7 +37957,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>数学与计算机科学学院</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -37960,11 +37966,11 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="L77" s="2" t="n">
@@ -37976,7 +37982,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -37986,7 +37992,7 @@
       </c>
       <c r="Q77" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -38006,12 +38012,12 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>浙江农林大学</t>
+          <t>上海电机学院</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -38026,7 +38032,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>数学与计算机科学学院</t>
+          <t>电子信息学院</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -38035,23 +38041,23 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L78" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M78" s="2" t="n"/>
       <c r="N78" s="2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -38061,7 +38067,7 @@
       </c>
       <c r="Q78" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -38081,12 +38087,12 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>上海电机学院</t>
+          <t>江苏师范大学</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -38101,7 +38107,7 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>电子信息学院</t>
+          <t>智慧教育学院（计算机科学与技术学院）</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -38126,7 +38132,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -38136,7 +38142,7 @@
       </c>
       <c r="Q79" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -38156,12 +38162,12 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>江苏师范大学</t>
+          <t>江西财经大学</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -38176,7 +38182,7 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>智慧教育学院（计算机科学与技术学院）</t>
+          <t>计算机与人工智能学院+信息管理学院</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -38201,7 +38207,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -38211,7 +38217,7 @@
       </c>
       <c r="Q80" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -38231,12 +38237,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>江西财经大学</t>
+          <t>浙江财经大学</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -38251,7 +38257,7 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院+信息管理学院</t>
+          <t>信息管理人工智能学院</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -38306,7 +38312,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>浙江财经大学</t>
+          <t>温州大学</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -38326,7 +38332,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>信息管理人工智能学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -38381,12 +38387,12 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>温州大学</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -38401,7 +38407,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -38410,23 +38416,23 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="L83" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M83" s="2" t="n"/>
       <c r="N83" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -38436,7 +38442,7 @@
       </c>
       <c r="Q83" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -38456,17 +38462,17 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>天津师范大学</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -38476,7 +38482,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -38501,7 +38507,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -38511,7 +38517,7 @@
       </c>
       <c r="Q84" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -38531,17 +38537,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>天津师范大学</t>
+          <t>安徽建筑大学</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -38551,7 +38557,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>电子与信息工程学院</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -38560,11 +38566,11 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L85" s="2" t="n">
@@ -38606,12 +38612,12 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>安徽建筑大学</t>
+          <t>江西理工大学</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -38626,7 +38632,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>电子与信息工程学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -38635,11 +38641,11 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="L86" s="2" t="n">
@@ -38651,7 +38657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -38661,7 +38667,7 @@
       </c>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -38681,12 +38687,12 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>江西理工大学</t>
+          <t>浙江工业大学</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -38701,7 +38707,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>地理信息学院</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -38710,11 +38716,11 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="L87" s="2" t="n">
@@ -38726,7 +38732,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -38736,7 +38742,7 @@
       </c>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -38756,7 +38762,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>浙江工业大学</t>
+          <t>浙江科技大学</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -38776,7 +38782,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>地理信息学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -38785,11 +38791,11 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
@@ -38801,7 +38807,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -38811,7 +38817,7 @@
       </c>
       <c r="Q88" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -38831,17 +38837,17 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>浙江科技大学</t>
+          <t>中国民航大学</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -38851,7 +38857,7 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>电子信息与自动化学院</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -38868,15 +38874,15 @@
         </is>
       </c>
       <c r="L89" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M89" s="2" t="n"/>
       <c r="N89" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -38886,7 +38892,7 @@
       </c>
       <c r="Q89" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -38906,12 +38912,12 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>中国民航大学</t>
+          <t>北京印刷学院</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -38926,7 +38932,7 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>电子信息与自动化学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -38951,7 +38957,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -38961,7 +38967,7 @@
       </c>
       <c r="Q90" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -38981,7 +38987,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>北京印刷学院</t>
+          <t>北京工商大学</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -39001,7 +39007,7 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -39056,7 +39062,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>北京工商大学</t>
+          <t>北京物资学院</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -39101,7 +39107,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -39111,7 +39117,7 @@
       </c>
       <c r="Q92" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -39131,7 +39137,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>北京物资学院</t>
+          <t>北京联合大学</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -39151,7 +39157,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>智慧城市学院</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -39176,7 +39182,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -39186,7 +39192,7 @@
       </c>
       <c r="Q93" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -39206,12 +39212,12 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>北京联合大学</t>
+          <t>天津财经大学</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>天津</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -39226,7 +39232,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>智慧城市学院</t>
+          <t>理工学院</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -39251,7 +39257,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -39261,7 +39267,7 @@
       </c>
       <c r="Q94" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -39281,17 +39287,17 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>天津财经大学</t>
+          <t>安徽农业大学</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>天津</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -39301,7 +39307,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>理工学院</t>
+          <t>信息与计算机学院</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -39326,7 +39332,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -39336,7 +39342,7 @@
       </c>
       <c r="Q95" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -39356,7 +39362,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>安徽农业大学</t>
+          <t>安徽理工大学</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -39376,7 +39382,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>信息与计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -39401,7 +39407,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>✅22408兼容；含AI</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -39411,7 +39417,7 @@
       </c>
       <c r="Q96" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
         </is>
       </c>
     </row>
@@ -39431,12 +39437,12 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>安徽理工大学</t>
+          <t>山东工商学院</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -39451,7 +39457,7 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -39476,7 +39482,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含AI</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -39486,7 +39492,7 @@
       </c>
       <c r="Q97" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含AI</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -39506,17 +39512,17 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>山东工商学院</t>
+          <t>山西大学</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
@@ -39526,7 +39532,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机与信息技术学院</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -39551,7 +39557,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>✅22408兼容；含电子信息</t>
+          <t>⚠️非22408(英一数一408)</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -39561,7 +39567,7 @@
       </c>
       <c r="Q98" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
+          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
         </is>
       </c>
     </row>
@@ -39581,17 +39587,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>山西大学</t>
+          <t>江西中医药大学</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -39601,7 +39607,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息技术学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -39626,7 +39632,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>⚠️非22408(英一数一408)</t>
+          <t>✅22408兼容；含电子信息</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -39636,7 +39642,7 @@
       </c>
       <c r="Q99" s="2" t="inlineStr">
         <is>
-          <t>N诺候选数据（未三源人工核对）；⚠️非22408(英一数一408)</t>
+          <t>N诺候选数据（未三源人工核对）；✅22408兼容；含电子信息</t>
         </is>
       </c>
     </row>
@@ -52457,12 +52463,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>江西中医药大学</t>
+          <t>海南师范大学</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -52472,7 +52478,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -52488,7 +52494,7 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -52520,8 +52526,10 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P76" s="2" t="n">
-        <v>284</v>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q76" s="2" t="n">
         <v>32</v>
@@ -52535,12 +52543,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>海南师范大学</t>
+          <t>湖北汽车工业学院</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -52550,7 +52558,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>智能网联汽车学院</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -52566,7 +52574,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -52583,25 +52591,19 @@
         <v>1</v>
       </c>
       <c r="L77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O77" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P77" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>297</v>
+      </c>
+      <c r="O77" s="2" t="n">
+        <v>290</v>
+      </c>
+      <c r="P77" s="2" t="n">
+        <v>294</v>
       </c>
       <c r="Q77" s="2" t="n">
         <v>32</v>
@@ -52615,12 +52617,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>湖北汽车工业学院</t>
+          <t>西安建筑科技大学</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>西北</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -52630,7 +52632,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>智能网联汽车学院</t>
+          <t>信息与控制工程学院</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -52644,11 +52646,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="H78" s="2" t="n"/>
       <c r="I78" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -52663,19 +52661,25 @@
         <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N78" s="2" t="n">
-        <v>297</v>
-      </c>
-      <c r="O78" s="2" t="n">
-        <v>290</v>
-      </c>
-      <c r="P78" s="2" t="n">
-        <v>294</v>
+        <v>34</v>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q78" s="2" t="n">
         <v>32</v>
@@ -52689,12 +52693,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>西安建筑科技大学</t>
+          <t>华北理工大学</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -52704,21 +52708,27 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>信息与控制工程学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n"/>
+          <t>22408</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>264</v>
+      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="n"/>
+          <t>=国家线</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -52733,10 +52743,10 @@
         <v>1</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -52748,24 +52758,22 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P79" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="P79" s="2" t="n">
+        <v>293</v>
       </c>
       <c r="Q79" s="2" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>华北理工大学</t>
+          <t>呼和浩特民族学院</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -52780,16 +52788,16 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机与信息技术学院</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -52798,12 +52806,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>大量调剂</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -52811,14 +52819,20 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="M80" s="2" t="n">
-        <v>2</v>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
@@ -52830,11 +52844,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P80" s="2" t="n">
-        <v>293</v>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q80" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
@@ -52845,12 +52861,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>呼和浩特民族学院</t>
+          <t>桂林电子科技大学</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -52860,12 +52876,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息技术学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -52878,12 +52894,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16+16南宁研究院</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>大量调剂</t>
+          <t>一志愿19人，缺口大</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -52891,38 +52907,26 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K81" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="O81" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="P81" s="2" t="n">
+        <v>298</v>
       </c>
       <c r="Q81" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="R81" s="2" t="inlineStr">
         <is>
@@ -52933,12 +52937,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>桂林电子科技大学</t>
+          <t>西南民族大学</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -52948,7 +52952,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -52957,7 +52961,7 @@
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -52966,12 +52970,12 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>16+16南宁研究院</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>一志愿19人，缺口大</t>
+          <t>调剂</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -52980,22 +52984,22 @@
         </is>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>364</v>
+        <v>293</v>
       </c>
       <c r="O82" s="2" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="P82" s="2" t="n">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="Q82" s="2" t="n">
         <v>9</v>
@@ -53009,12 +53013,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>西南民族大学</t>
+          <t>新疆农业大学</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>西北</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -53024,7 +53028,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -53033,7 +53037,7 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -53042,12 +53046,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>调剂</t>
+          <t>一志愿为主</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -53059,22 +53063,22 @@
         <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>293</v>
+        <v>335</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>267</v>
+        <v>304</v>
       </c>
       <c r="P83" s="2" t="n">
-        <v>279</v>
+        <v>322</v>
       </c>
       <c r="Q83" s="2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R83" s="2" t="inlineStr">
         <is>
@@ -53085,12 +53089,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>新疆农业大学</t>
+          <t>北京电子科技学院</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>西北</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -53100,30 +53104,30 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>N诺</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+18</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>一志愿为主</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -53132,41 +53136,41 @@
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="L84" s="2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="P84" s="2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q84" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R84" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>北京电子科技学院</t>
+          <t>重庆科技大学</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -53176,30 +53180,30 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>计算机科学与工程学院（人工智能学院）</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>+18</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>大量调剂</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -53208,41 +53212,41 @@
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>385</v>
+        <v>319</v>
       </c>
       <c r="O85" s="2" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="P85" s="2" t="n">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="Q85" s="2" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="R85" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>重庆科技大学</t>
+          <t>安徽工业大学</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -53252,30 +53256,30 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与工程学院（人工智能学院）</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+30</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>大量调剂</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -53284,36 +53288,40 @@
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="N86" s="2" t="n">
-        <v>319</v>
-      </c>
-      <c r="O86" s="2" t="n">
-        <v>275</v>
+        <v>62</v>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P86" s="2" t="n">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="Q86" s="2" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="R86" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>安徽工业大学</t>
+          <t>杭州师范大学</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -53328,7 +53336,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>工学院</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -53337,16 +53345,16 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>+30</t>
+          <t>+20</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -53360,29 +53368,25 @@
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="L87" s="2" t="n">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O87" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="O87" s="2" t="n">
+        <v>285</v>
       </c>
       <c r="P87" s="2" t="n">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="Q87" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R87" s="2" t="inlineStr">
         <is>
@@ -53393,7 +53397,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>杭州师范大学</t>
+          <t>苏州科技大学</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -53408,7 +53412,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>工学院</t>
+          <t>电子与信息工程学院</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -53417,16 +53421,16 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>+20</t>
+          <t>+36</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -53440,25 +53444,25 @@
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="O88" s="2" t="n">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="P88" s="2" t="n">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="Q88" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R88" s="2" t="inlineStr">
         <is>
@@ -53469,12 +53473,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>苏州科技大学</t>
+          <t>长沙理工大学</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -53484,7 +53488,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>电子与信息工程学院</t>
+          <t>计算机与通信工程学院</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -53493,16 +53497,16 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>+36</t>
+          <t>+25</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -53516,25 +53520,25 @@
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>378</v>
+        <v>397</v>
       </c>
       <c r="O89" s="2" t="n">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="P89" s="2" t="n">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q89" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R89" s="2" t="inlineStr">
         <is>
@@ -53545,12 +53549,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>长沙理工大学</t>
+          <t>厦门理工学院</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -53560,30 +53564,30 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>计算机与通信工程学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>非408</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>289</v>
+        <v>264</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>+25</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>调剂</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -53592,41 +53596,41 @@
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>167</v>
+        <v>31</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>397</v>
+        <v>343</v>
       </c>
       <c r="O90" s="2" t="n">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="P90" s="2" t="n">
-        <v>332</v>
+        <v>293</v>
       </c>
       <c r="Q90" s="2" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="R90" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>机构估算</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>厦门理工学院</t>
+          <t>中南林业科技大学</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -53636,30 +53640,26 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>低空经济学院</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>非408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
+          <t>+14</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n"/>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>调剂</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -53668,41 +53668,45 @@
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>343</v>
-      </c>
-      <c r="O91" s="2" t="n">
-        <v>274</v>
+        <v>20</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P91" s="2" t="n">
-        <v>293</v>
+        <v>338</v>
       </c>
       <c r="Q91" s="2" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="R91" s="2" t="inlineStr">
         <is>
-          <t>机构估算</t>
+          <t>N诺</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>中南林业科技大学</t>
+          <t>石家庄铁道大学</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -53712,7 +53716,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>低空经济学院</t>
+          <t>信息科学与技术学院</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -53721,14 +53725,18 @@
         </is>
       </c>
       <c r="F92" s="2" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="n"/>
+          <t>+17</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -53740,13 +53748,13 @@
         </is>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="L92" s="2" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="M92" s="2" t="n">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
@@ -53759,7 +53767,7 @@
         </is>
       </c>
       <c r="P92" s="2" t="n">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="Q92" s="2" t="n">
         <v>27</v>
@@ -53773,12 +53781,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>石家庄铁道大学</t>
+          <t>中国民用航空飞行学院</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -53788,30 +53796,30 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>信息科学与技术学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22408</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>+17</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>大量调剂</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -53820,45 +53828,41 @@
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="M93" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N93" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O93" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>272</v>
+      </c>
+      <c r="O93" s="2" t="n">
+        <v>272</v>
       </c>
       <c r="P93" s="2" t="n">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="Q93" s="2" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="R93" s="2" t="inlineStr">
         <is>
-          <t>N诺</t>
+          <t>官方</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>中国民用航空飞行学院</t>
+          <t>太原科技大学</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -53868,30 +53872,30 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+23</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>大量调剂</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -53903,38 +53907,38 @@
         <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>272</v>
+        <v>375</v>
       </c>
       <c r="O94" s="2" t="n">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="P94" s="2" t="n">
-        <v>272</v>
+        <v>328</v>
       </c>
       <c r="Q94" s="2" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="R94" s="2" t="inlineStr">
         <is>
-          <t>官方</t>
+          <t>N诺</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>太原科技大学</t>
+          <t>武汉工程大学</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -53944,7 +53948,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机科学与工程学院（人工智能学院）</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -53953,16 +53957,16 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>+23</t>
+          <t>+21</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -53979,22 +53983,22 @@
         <v>1</v>
       </c>
       <c r="L95" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M95" s="2" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>375</v>
+        <v>296</v>
       </c>
       <c r="O95" s="2" t="n">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="P95" s="2" t="n">
-        <v>328</v>
+        <v>285</v>
       </c>
       <c r="Q95" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R95" s="2" t="inlineStr">
         <is>
@@ -54005,12 +54009,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>武汉工程大学</t>
+          <t>天津职业技术师范大学</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -54020,7 +54024,7 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与工程学院（人工智能学院）</t>
+          <t>信息技术工程学院</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -54029,16 +54033,16 @@
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>+21</t>
+          <t>+17</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -54061,16 +54065,16 @@
         <v>3</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>296</v>
+        <v>349</v>
       </c>
       <c r="O96" s="2" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="P96" s="2" t="n">
-        <v>285</v>
+        <v>321</v>
       </c>
       <c r="Q96" s="2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R96" s="2" t="inlineStr">
         <is>
@@ -54081,12 +54085,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>天津职业技术师范大学</t>
+          <t>上海海洋大学</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -54096,7 +54100,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>信息技术工程学院</t>
+          <t>信息学院</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -54105,16 +54109,16 @@
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>+17</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>136</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -54127,26 +54131,30 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K97" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>3</v>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>349</v>
+        <v>386</v>
       </c>
       <c r="O97" s="2" t="n">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="P97" s="2" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="Q97" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="R97" s="2" t="inlineStr">
         <is>
@@ -54157,7 +54165,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>上海海洋大学</t>
+          <t>上海科技大学</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -54172,7 +54180,7 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>信息学院</t>
+          <t>信息科学与技术学院</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -54190,7 +54198,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -54213,17 +54221,25 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M98" s="2" t="n">
-        <v>136</v>
-      </c>
-      <c r="N98" s="2" t="n">
-        <v>386</v>
-      </c>
-      <c r="O98" s="2" t="n">
-        <v>276</v>
-      </c>
-      <c r="P98" s="2" t="n">
-        <v>317</v>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q98" s="2" t="n">
         <v>19</v>
@@ -54237,7 +54253,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>上海科技大学</t>
+          <t>中国计量大学</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -54252,7 +54268,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>信息科学与技术学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -54261,16 +54277,16 @@
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -54283,35 +54299,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P99" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K99" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>343</v>
+      </c>
+      <c r="O99" s="2" t="n">
+        <v>284</v>
+      </c>
+      <c r="P99" s="2" t="n">
+        <v>306</v>
       </c>
       <c r="Q99" s="2" t="n">
         <v>19</v>
@@ -54325,7 +54329,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>中国计量大学</t>
+          <t>南京财经大学</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -54340,7 +54344,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -54349,16 +54353,16 @@
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -54371,23 +54375,33 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K100" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>35</v>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="N100" s="2" t="n">
-        <v>343</v>
-      </c>
-      <c r="O100" s="2" t="n">
-        <v>284</v>
-      </c>
-      <c r="P100" s="2" t="n">
-        <v>306</v>
+        <v>6</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q100" s="2" t="n">
         <v>19</v>
@@ -54401,12 +54415,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>南京财经大学</t>
+          <t>天津农学院</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -54416,7 +54430,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -54425,16 +54439,16 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -54452,13 +54466,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L101" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M101" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
@@ -54487,12 +54499,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>天津农学院</t>
+          <t>河南农业大学</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -54502,7 +54514,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>信息与管理科学学院</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -54520,7 +54532,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -54533,31 +54545,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="K102" s="2" t="n">
+        <v>1.5</v>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O102" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P102" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>315</v>
+      </c>
+      <c r="O102" s="2" t="n">
+        <v>274</v>
+      </c>
+      <c r="P102" s="2" t="n">
+        <v>295</v>
       </c>
       <c r="Q102" s="2" t="n">
         <v>19</v>
@@ -54571,7 +54575,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>河南农业大学</t>
+          <t>河南理工大学</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -54586,7 +54590,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>信息与管理科学学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -54595,16 +54599,16 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -54618,25 +54622,29 @@
         </is>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L103" s="2" t="n">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="M103" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N103" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="n">
         <v>315</v>
       </c>
-      <c r="O103" s="2" t="n">
-        <v>274</v>
-      </c>
-      <c r="P103" s="2" t="n">
-        <v>295</v>
-      </c>
       <c r="Q103" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
@@ -54647,12 +54655,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>河南理工大学</t>
+          <t>浙江农林大学</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -54662,7 +54670,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>数学与计算机科学学院</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -54671,16 +54679,16 @@
         </is>
       </c>
       <c r="F104" s="2" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -54694,29 +54702,25 @@
         </is>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="L104" s="2" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="M104" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O104" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>395</v>
+      </c>
+      <c r="O104" s="2" t="n">
+        <v>278</v>
       </c>
       <c r="P104" s="2" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="Q104" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R104" s="2" t="inlineStr">
         <is>
@@ -54727,12 +54731,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>浙江农林大学</t>
+          <t>西南石油大学</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -54742,7 +54746,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>数学与计算机科学学院</t>
+          <t>计算机科学学院</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -54751,16 +54755,16 @@
         </is>
       </c>
       <c r="F105" s="2" t="n">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -54774,22 +54778,22 @@
         </is>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="L105" s="2" t="n">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="M105" s="2" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="N105" s="2" t="n">
         <v>395</v>
       </c>
       <c r="O105" s="2" t="n">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="P105" s="2" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q105" s="2" t="n">
         <v>19</v>
@@ -54803,12 +54807,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>西南石油大学</t>
+          <t>南华大学</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -54818,7 +54822,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>计算机科学学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -54827,16 +54831,16 @@
         </is>
       </c>
       <c r="F106" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -54850,25 +54854,25 @@
         </is>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L106" s="2" t="n">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="M106" s="2" t="n">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>395</v>
+        <v>331</v>
       </c>
       <c r="O106" s="2" t="n">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="P106" s="2" t="n">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="Q106" s="2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R106" s="2" t="inlineStr">
         <is>
@@ -54879,12 +54883,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>南华大学</t>
+          <t>广西民族大学</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -54894,7 +54898,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -54903,16 +54907,16 @@
         </is>
       </c>
       <c r="F107" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -54926,22 +54930,22 @@
         </is>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="M107" s="2" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="O107" s="2" t="n">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="P107" s="2" t="n">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="Q107" s="2" t="n">
         <v>16</v>
@@ -54955,12 +54959,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>广西民族大学</t>
+          <t>湘潭大学</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -54970,7 +54974,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机学院/网络空间安全学院</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -54983,12 +54987,12 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>+10</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -55002,22 +55006,22 @@
         </is>
       </c>
       <c r="K108" s="2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="L108" s="2" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="O108" s="2" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="P108" s="2" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="Q108" s="2" t="n">
         <v>16</v>
@@ -55031,12 +55035,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>湘潭大学</t>
+          <t>上海电机学院</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -55046,7 +55050,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>计算机学院/网络空间安全学院</t>
+          <t>电子信息学院</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -55064,7 +55068,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -55078,25 +55082,25 @@
         </is>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L109" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M109" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>326</v>
+      </c>
+      <c r="O109" s="2" t="n">
+        <v>281</v>
+      </c>
+      <c r="P109" s="2" t="n">
+        <v>309</v>
+      </c>
+      <c r="Q109" s="2" t="n">
         <v>15</v>
-      </c>
-      <c r="N109" s="2" t="n">
-        <v>358</v>
-      </c>
-      <c r="O109" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="P109" s="2" t="n">
-        <v>295</v>
-      </c>
-      <c r="Q109" s="2" t="n">
-        <v>16</v>
       </c>
       <c r="R109" s="2" t="inlineStr">
         <is>
@@ -55107,7 +55111,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>上海电机学院</t>
+          <t>江苏师范大学</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -55122,7 +55126,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>电子信息学院</t>
+          <t>智慧教育学院（计算机科学与技术学院）</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -55140,7 +55144,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -55157,19 +55161,19 @@
         <v>1.2</v>
       </c>
       <c r="L110" s="2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M110" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="O110" s="2" t="n">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="P110" s="2" t="n">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="Q110" s="2" t="n">
         <v>15</v>
@@ -55183,7 +55187,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>江苏师范大学</t>
+          <t>江西财经大学</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -55198,7 +55202,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>智慧教育学院（计算机科学与技术学院）</t>
+          <t>计算机与人工智能学院+信息管理学院</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -55216,7 +55220,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -55233,19 +55237,19 @@
         <v>1.2</v>
       </c>
       <c r="L111" s="2" t="n">
-        <v>14</v>
+        <v>205</v>
       </c>
       <c r="M111" s="2" t="n">
-        <v>12</v>
+        <v>168</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>321</v>
+        <v>380</v>
       </c>
       <c r="O111" s="2" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P111" s="2" t="n">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="Q111" s="2" t="n">
         <v>15</v>
@@ -55259,7 +55263,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>江西财经大学</t>
+          <t>浙江财经大学</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -55274,7 +55278,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院+信息管理学院</t>
+          <t>信息管理人工智能学院</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -55292,7 +55296,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>49</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -55309,19 +55313,19 @@
         <v>1.2</v>
       </c>
       <c r="L112" s="2" t="n">
-        <v>205</v>
+        <v>59</v>
       </c>
       <c r="M112" s="2" t="n">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="O112" s="2" t="n">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="P112" s="2" t="n">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="Q112" s="2" t="n">
         <v>15</v>
@@ -55335,7 +55339,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>浙江财经大学</t>
+          <t>温州大学</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -55350,7 +55354,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>信息管理人工智能学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -55368,7 +55372,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -55385,13 +55389,13 @@
         <v>1.2</v>
       </c>
       <c r="L113" s="2" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="M113" s="2" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>409</v>
+        <v>365</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>264</v>
@@ -55411,7 +55415,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>温州大学</t>
+          <t>上海海事大学</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -55426,7 +55430,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -55435,16 +55439,16 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -55458,25 +55462,31 @@
         </is>
       </c>
       <c r="K114" s="2" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="M114" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="N114" s="2" t="n">
-        <v>365</v>
-      </c>
-      <c r="O114" s="2" t="n">
-        <v>264</v>
-      </c>
-      <c r="P114" s="2" t="n">
-        <v>309</v>
+        <v>27</v>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q114" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R114" s="2" t="inlineStr">
         <is>
@@ -55487,12 +55497,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>上海海事大学</t>
+          <t>佛山大学</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -55502,7 +55512,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>电子信息工程学院</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -55511,16 +55521,16 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -55534,28 +55544,22 @@
         </is>
       </c>
       <c r="K115" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L115" s="2" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="M115" s="2" t="n">
-        <v>27</v>
-      </c>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P115" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>376</v>
+      </c>
+      <c r="O115" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="P115" s="2" t="n">
+        <v>305</v>
       </c>
       <c r="Q115" s="2" t="n">
         <v>13</v>
@@ -55569,12 +55573,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>佛山大学</t>
+          <t>天津师范大学</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -55584,7 +55588,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>电子信息工程学院</t>
+          <t>计算机与信息工程学院</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -55593,16 +55597,16 @@
         </is>
       </c>
       <c r="F116" s="2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -55616,19 +55620,19 @@
         </is>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L116" s="2" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="M116" s="2" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="O116" s="2" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P116" s="2" t="n">
         <v>305</v>
@@ -55645,12 +55649,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>天津师范大学</t>
+          <t>安徽建筑大学</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -55660,7 +55664,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息工程学院</t>
+          <t>电子与信息工程学院</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -55669,16 +55673,16 @@
         </is>
       </c>
       <c r="F117" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -55692,22 +55696,22 @@
         </is>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L117" s="2" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="M117" s="2" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="O117" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="P117" s="2" t="n">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="Q117" s="2" t="n">
         <v>13</v>
@@ -55721,7 +55725,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>安徽建筑大学</t>
+          <t>江西理工大学</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -55736,7 +55740,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>电子与信息工程学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -55745,16 +55749,16 @@
         </is>
       </c>
       <c r="F118" s="2" t="n">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -55768,22 +55772,22 @@
         </is>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="M118" s="2" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>264</v>
       </c>
       <c r="P118" s="2" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q118" s="2" t="n">
         <v>13</v>
@@ -55797,7 +55801,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>江西理工大学</t>
+          <t>浙江工业大学</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -55812,7 +55816,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>地理信息学院</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -55821,16 +55825,16 @@
         </is>
       </c>
       <c r="F119" s="2" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -55847,19 +55851,19 @@
         <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="M119" s="2" t="n">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>357</v>
+        <v>405</v>
       </c>
       <c r="O119" s="2" t="n">
-        <v>264</v>
+        <v>300</v>
       </c>
       <c r="P119" s="2" t="n">
-        <v>298</v>
+        <v>335</v>
       </c>
       <c r="Q119" s="2" t="n">
         <v>13</v>
@@ -55873,7 +55877,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>浙江工业大学</t>
+          <t>浙江科技大学</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -55888,7 +55892,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>地理信息学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -55897,16 +55901,16 @@
         </is>
       </c>
       <c r="F120" s="2" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -55920,22 +55924,22 @@
         </is>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="L120" s="2" t="n">
-        <v>222</v>
+        <v>58</v>
       </c>
       <c r="M120" s="2" t="n">
-        <v>179</v>
+        <v>54</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>405</v>
+        <v>365</v>
       </c>
       <c r="O120" s="2" t="n">
+        <v>264</v>
+      </c>
+      <c r="P120" s="2" t="n">
         <v>300</v>
-      </c>
-      <c r="P120" s="2" t="n">
-        <v>335</v>
       </c>
       <c r="Q120" s="2" t="n">
         <v>13</v>
@@ -55949,12 +55953,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>浙江科技大学</t>
+          <t>西南科技大学</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -55982,7 +55986,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
@@ -55999,19 +56003,19 @@
         <v>1.1</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="M121" s="2" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="O121" s="2" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="P121" s="2" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="Q121" s="2" t="n">
         <v>13</v>
@@ -56025,12 +56029,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>西南科技大学</t>
+          <t>中南民族大学</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -56040,7 +56044,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -56058,7 +56062,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
@@ -56072,25 +56076,25 @@
         </is>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="M122" s="2" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>384</v>
+        <v>270</v>
       </c>
       <c r="O122" s="2" t="n">
+        <v>265</v>
+      </c>
+      <c r="P122" s="2" t="n">
         <v>268</v>
       </c>
-      <c r="P122" s="2" t="n">
-        <v>305</v>
-      </c>
       <c r="Q122" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R122" s="2" t="inlineStr">
         <is>
@@ -56101,12 +56105,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>中南民族大学</t>
+          <t>中国民航大学</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -56116,7 +56120,7 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>电子信息与自动化学院</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -56134,7 +56138,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr">
@@ -56151,19 +56155,19 @@
         <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="N123" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="O123" s="2" t="n">
         <v>270</v>
       </c>
-      <c r="O123" s="2" t="n">
-        <v>265</v>
-      </c>
       <c r="P123" s="2" t="n">
-        <v>268</v>
+        <v>294</v>
       </c>
       <c r="Q123" s="2" t="n">
         <v>12</v>
@@ -56177,7 +56181,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>中国民航大学</t>
+          <t>北京印刷学院</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -56192,7 +56196,7 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>电子信息与自动化学院</t>
+          <t>信息工程学院</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -56210,7 +56214,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
@@ -56227,19 +56231,19 @@
         <v>1</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="M124" s="2" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>383</v>
+        <v>319</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="P124" s="2" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Q124" s="2" t="n">
         <v>12</v>
@@ -56253,7 +56257,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>北京印刷学院</t>
+          <t>北京工商大学</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -56268,7 +56272,7 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>信息工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -56286,7 +56290,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr">
@@ -56303,19 +56307,19 @@
         <v>1</v>
       </c>
       <c r="L125" s="2" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="M125" s="2" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>319</v>
+        <v>376</v>
       </c>
       <c r="O125" s="2" t="n">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="P125" s="2" t="n">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q125" s="2" t="n">
         <v>12</v>
@@ -56329,7 +56333,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>北京工商大学</t>
+          <t>北京物资学院</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -56362,7 +56366,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
@@ -56379,19 +56383,25 @@
         <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="M126" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="N126" s="2" t="n">
-        <v>376</v>
-      </c>
-      <c r="O126" s="2" t="n">
-        <v>266</v>
-      </c>
-      <c r="P126" s="2" t="n">
-        <v>307</v>
+        <v>2</v>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P126" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q126" s="2" t="n">
         <v>12</v>
@@ -56405,7 +56415,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>北京物资学院</t>
+          <t>北京联合大学</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -56420,7 +56430,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>智慧城市学院</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -56438,7 +56448,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr">
@@ -56455,25 +56465,19 @@
         <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N127" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O127" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P127" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="N127" s="2" t="n">
+        <v>288</v>
+      </c>
+      <c r="O127" s="2" t="n">
+        <v>267</v>
+      </c>
+      <c r="P127" s="2" t="n">
+        <v>278</v>
       </c>
       <c r="Q127" s="2" t="n">
         <v>12</v>
@@ -56487,7 +56491,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>北京联合大学</t>
+          <t>天津财经大学</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -56502,7 +56506,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>智慧城市学院</t>
+          <t>理工学院</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -56520,7 +56524,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
@@ -56537,19 +56541,23 @@
         <v>1</v>
       </c>
       <c r="L128" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M128" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="N128" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="O128" s="2" t="n">
-        <v>267</v>
+        <v>1</v>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P128" s="2" t="n">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="Q128" s="2" t="n">
         <v>12</v>
@@ -56563,12 +56571,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>天津财经大学</t>
+          <t>安徽农业大学</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -56578,7 +56586,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>理工学院</t>
+          <t>信息与计算机学院</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -56596,7 +56604,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr">
@@ -56613,23 +56621,19 @@
         <v>1</v>
       </c>
       <c r="L129" s="2" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="M129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N129" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O129" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>56</v>
+      </c>
+      <c r="N129" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="O129" s="2" t="n">
+        <v>264</v>
       </c>
       <c r="P129" s="2" t="n">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="Q129" s="2" t="n">
         <v>12</v>
@@ -56643,7 +56647,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>安徽农业大学</t>
+          <t>安徽理工大学</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -56658,7 +56662,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>信息与计算机学院</t>
+          <t>人工智能学院</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -56676,7 +56680,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>148</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
@@ -56693,19 +56697,19 @@
         <v>1</v>
       </c>
       <c r="L130" s="2" t="n">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="M130" s="2" t="n">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="O130" s="2" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="P130" s="2" t="n">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="Q130" s="2" t="n">
         <v>12</v>
@@ -56719,7 +56723,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>安徽理工大学</t>
+          <t>山东工商学院</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -56734,7 +56738,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>人工智能学院</t>
+          <t>计算机科学与技术学院</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -56752,7 +56756,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
@@ -56769,19 +56773,19 @@
         <v>1</v>
       </c>
       <c r="L131" s="2" t="n">
-        <v>180</v>
+        <v>5</v>
       </c>
       <c r="M131" s="2" t="n">
-        <v>148</v>
+        <v>5</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="O131" s="2" t="n">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="P131" s="2" t="n">
-        <v>319</v>
+        <v>303</v>
       </c>
       <c r="Q131" s="2" t="n">
         <v>12</v>
@@ -56795,12 +56799,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>山东工商学院</t>
+          <t>山西大学</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>华东</t>
+          <t>华北</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -56810,7 +56814,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与技术学院</t>
+          <t>计算机与信息技术学院</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -56828,7 +56832,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
@@ -56845,19 +56849,19 @@
         <v>1</v>
       </c>
       <c r="L132" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="M132" s="2" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="O132" s="2" t="n">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="P132" s="2" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="Q132" s="2" t="n">
         <v>12</v>
@@ -56871,12 +56875,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>山西大学</t>
+          <t>广西师范大学</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>华北</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -56886,7 +56890,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>计算机与信息技术学院</t>
+          <t>计算机科学与信息工程学院</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -56895,7 +56899,7 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -56904,7 +56908,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
@@ -56921,19 +56925,19 @@
         <v>1</v>
       </c>
       <c r="L133" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M133" s="2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="O133" s="2" t="n">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="P133" s="2" t="n">
-        <v>313</v>
+        <v>279</v>
       </c>
       <c r="Q133" s="2" t="n">
         <v>12</v>
@@ -56947,12 +56951,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>广西师范大学</t>
+          <t>成都大学</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>西南</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -56962,7 +56966,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与信息工程学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -56971,16 +56975,16 @@
         </is>
       </c>
       <c r="F134" s="2" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>=国家线</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
@@ -56997,19 +57001,19 @@
         <v>1</v>
       </c>
       <c r="L134" s="2" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="M134" s="2" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="N134" s="2" t="n">
         <v>332</v>
       </c>
       <c r="O134" s="2" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="P134" s="2" t="n">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="Q134" s="2" t="n">
         <v>12</v>
@@ -57023,12 +57027,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>成都大学</t>
+          <t>桂林理工大学</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>西南</t>
+          <t>华南</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -57038,7 +57042,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>计算机学院</t>
+          <t>计算机科学与工程学院</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -57047,16 +57051,16 @@
         </is>
       </c>
       <c r="F135" s="2" t="n">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>=国家线</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
@@ -57073,19 +57077,19 @@
         <v>1</v>
       </c>
       <c r="L135" s="2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="M135" s="2" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>332</v>
+        <v>289</v>
       </c>
       <c r="O135" s="2" t="n">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="P135" s="2" t="n">
-        <v>296</v>
+        <v>268</v>
       </c>
       <c r="Q135" s="2" t="n">
         <v>12</v>
@@ -57099,12 +57103,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>桂林理工大学</t>
+          <t>武汉纺织大学</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>华南</t>
+          <t>华中</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -57114,7 +57118,7 @@
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>计算机科学与工程学院</t>
+          <t>计算机与人工智能学院</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -57123,7 +57127,7 @@
         </is>
       </c>
       <c r="F136" s="2" t="n">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -57132,7 +57136,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
@@ -57149,19 +57153,19 @@
         <v>1</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>289</v>
+        <v>348</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="P136" s="2" t="n">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="Q136" s="2" t="n">
         <v>12</v>
@@ -57175,12 +57179,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>武汉纺织大学</t>
+          <t>江西中医药大学</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>华中</t>
+          <t>华东</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -57190,7 +57194,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>计算机与人工智能学院</t>
+          <t>计算机学院</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -57208,7 +57212,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
@@ -57225,19 +57229,23 @@
         <v>1</v>
       </c>
       <c r="L137" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="M137" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N137" s="2" t="n">
-        <v>348</v>
-      </c>
-      <c r="O137" s="2" t="n">
-        <v>268</v>
+        <v>1</v>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="P137" s="2" t="n">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="Q137" s="2" t="n">
         <v>12</v>
@@ -65816,10 +65824,8 @@
           <t>待确认</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E101" s="2" t="n">
+        <v>264</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -80631,10 +80637,8 @@
           <t>双非</t>
         </is>
       </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="D117" s="2" t="n">
+        <v>264</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
